--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486731_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486731_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.4287</v>
+        <v>9.4087</v>
       </c>
       <c r="E2" t="n">
-        <v>10.1541</v>
+        <v>7.8858</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2745</v>
+        <v>1.5229</v>
       </c>
       <c r="G2" t="n">
         <v>6.3871</v>
@@ -610,13 +610,13 @@
         <v>1.1585</v>
       </c>
       <c r="S2" t="n">
-        <v>3.0889</v>
+        <v>1.0689</v>
       </c>
       <c r="T2" t="n">
-        <v>3.6125</v>
+        <v>1.3441</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5236</v>
+        <v>-0.2753</v>
       </c>
       <c r="V2" t="n">
         <v>3.8834</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.0494</v>
+        <v>5.9141</v>
       </c>
       <c r="E3" t="n">
-        <v>3.866</v>
+        <v>4.7555</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1834</v>
+        <v>1.1586</v>
       </c>
       <c r="G3" t="n">
         <v>2.961</v>
@@ -688,13 +688,13 @@
         <v>1.7377</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3749</v>
+        <v>0.4897</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4969</v>
+        <v>0.3926</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1219</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="V3" t="n">
         <v>1.8842</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5222</v>
+        <v>3.8131</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6038</v>
+        <v>2.5967</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9184</v>
+        <v>1.2164</v>
       </c>
       <c r="G4" t="n">
         <v>3.6848</v>
@@ -766,13 +766,13 @@
         <v>1.9308</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.6493</v>
+        <v>-0.3584</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0209</v>
+        <v>-0.028</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6284</v>
+        <v>-0.3304</v>
       </c>
       <c r="V4" t="n">
         <v>-0.2856</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7094</v>
+        <v>1.3315</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2844</v>
+        <v>0.9811</v>
       </c>
       <c r="F5" t="n">
-        <v>0.425</v>
+        <v>0.3505</v>
       </c>
       <c r="G5" t="n">
         <v>-0.7761</v>
@@ -844,13 +844,13 @@
         <v>1.7377</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0261</v>
+        <v>0.6483</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9373</v>
+        <v>0.6339</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0888</v>
+        <v>0.0143</v>
       </c>
       <c r="V5" t="n">
         <v>-0.0852</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2447</v>
+        <v>0.7383999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8289</v>
+        <v>2.2977</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.5842</v>
+        <v>-1.5594</v>
       </c>
       <c r="G6" t="n">
         <v>0.2183</v>
@@ -922,13 +922,13 @@
         <v>0.7723</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.06619999999999999</v>
+        <v>0.4275</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2208</v>
+        <v>0.248</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1547</v>
+        <v>0.1795</v>
       </c>
       <c r="V6" t="n">
         <v>0.2856</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1532</v>
+        <v>-0.1035</v>
       </c>
       <c r="E7" t="n">
         <v>-0.0552</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.098</v>
+        <v>-0.0484</v>
       </c>
       <c r="G7" t="n">
         <v>-0.1311</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0221</v>
+        <v>0.0276</v>
       </c>
       <c r="T7" t="n">
         <v>-0.0552</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0331</v>
+        <v>0.0828</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7224</v>
+        <v>-0.3681</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4358</v>
+        <v>0.1917</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2866</v>
+        <v>-0.5597</v>
       </c>
       <c r="G8" t="n">
         <v>0.7146</v>
@@ -1078,13 +1078,13 @@
         <v>1.1585</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2093</v>
+        <v>0.145</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4416</v>
+        <v>0.1859</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2323</v>
+        <v>-0.0409</v>
       </c>
       <c r="V8" t="n">
         <v>-1.2277</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3438</v>
+        <v>-1.6444</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2854</v>
+        <v>-1.437</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0584</v>
+        <v>-0.2074</v>
       </c>
       <c r="G9" t="n">
         <v>-1.4927</v>
@@ -1156,13 +1156,13 @@
         <v>0.7723</v>
       </c>
       <c r="S9" t="n">
-        <v>1.3074</v>
+        <v>1.0067</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7169</v>
+        <v>0.5652</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5905</v>
+        <v>0.4415</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1871</v>
+        <v>-1.9458</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.221</v>
+        <v>-0.8556</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9661</v>
+        <v>-1.0902</v>
       </c>
       <c r="G10" t="n">
         <v>0.0198</v>
@@ -1234,13 +1234,13 @@
         <v>0.1931</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0554</v>
+        <v>0.2966</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2759</v>
+        <v>0.0895</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3313</v>
+        <v>0.2071</v>
       </c>
       <c r="V10" t="n">
         <v>-2.4554</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0876</v>
+        <v>-2.8559</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.3105</v>
+        <v>-3.1037</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2229</v>
+        <v>0.2478</v>
       </c>
       <c r="G11" t="n">
         <v>0.8265</v>
@@ -1312,13 +1312,13 @@
         <v>0.1931</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0167</v>
+        <v>0.2483</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.138</v>
+        <v>0.0688</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1547</v>
+        <v>0.1795</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2277</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4603</v>
+        <v>14.2881</v>
       </c>
       <c r="E12" t="n">
-        <v>12.4293</v>
+        <v>13.257</v>
       </c>
       <c r="F12" t="n">
-        <v>1.0309</v>
+        <v>1.0311</v>
       </c>
       <c r="G12" t="n">
         <v>12.4122</v>
@@ -1390,13 +1390,13 @@
         <v>9.654</v>
       </c>
       <c r="S12" t="n">
-        <v>3.172700000000001</v>
+        <v>4.0002</v>
       </c>
       <c r="T12" t="n">
-        <v>2.6174</v>
+        <v>3.4448</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5553</v>
+        <v>0.5552</v>
       </c>
       <c r="V12" t="n">
         <v>0.7715999999999998</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R. KOWALSKI</t>
+          <t>A. PUJADAS TARRADELLAS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6375</v>
+        <v>1.1603</v>
       </c>
       <c r="E13" t="n">
-        <v>2.7092</v>
+        <v>3.0103</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.0717</v>
+        <v>-1.85</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.6523</v>
+        <v>-1.4669</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.4886</v>
+        <v>-1.338</v>
       </c>
       <c r="I13" t="n">
-        <v>3.8363</v>
+        <v>-0.1288</v>
       </c>
       <c r="J13" t="n">
-        <v>2.3354</v>
+        <v>0.7000999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.143</v>
+        <v>0.7316</v>
       </c>
       <c r="L13" t="n">
-        <v>4.4784</v>
+        <v>-0.0315</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.9878</v>
+        <v>-2.167</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.3456</v>
+        <v>-2.0697</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.6421</v>
+        <v>-0.0973</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3862</v>
+        <v>1.1585</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.9308</v>
+        <v>-0.9654</v>
       </c>
       <c r="R13" t="n">
-        <v>2.3169</v>
+        <v>2.1239</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7725</v>
+        <v>-0.007</v>
       </c>
       <c r="T13" t="n">
-        <v>0.22</v>
+        <v>-0.4075</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.9925</v>
+        <v>0.4004</v>
       </c>
       <c r="V13" t="n">
-        <v>1.6761</v>
+        <v>1.4758</v>
       </c>
       <c r="W13" t="n">
-        <v>2.0845</v>
+        <v>3.6831</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.4084</v>
+        <v>-2.2073</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. PUJADAS TARRADELLAS</t>
+          <t>R. KOWALSKI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4612</v>
+        <v>1.003</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7001</v>
+        <v>2.3989</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.2389</v>
+        <v>-1.396</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.4669</v>
+        <v>-0.6523</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.338</v>
+        <v>-4.4886</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1288</v>
+        <v>3.8363</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7000999999999999</v>
+        <v>2.3354</v>
       </c>
       <c r="K14" t="n">
-        <v>0.7316</v>
+        <v>-2.143</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.0315</v>
+        <v>4.4784</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.167</v>
+        <v>-2.9878</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.0697</v>
+        <v>-2.3456</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.0973</v>
+        <v>-0.6421</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1585</v>
+        <v>0.3862</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1239</v>
+        <v>2.3169</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7062</v>
+        <v>-0.407</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7177</v>
+        <v>-0.0902</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0116</v>
+        <v>-0.3168</v>
       </c>
       <c r="V14" t="n">
-        <v>1.4758</v>
+        <v>1.6761</v>
       </c>
       <c r="W14" t="n">
-        <v>3.6831</v>
+        <v>2.0845</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.2073</v>
+        <v>-0.4084</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.313</v>
+        <v>0.4413</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.0345</v>
+        <v>0.0689</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3475</v>
+        <v>0.3724</v>
       </c>
       <c r="G15" t="n">
         <v>0.2965</v>
@@ -1624,13 +1624,13 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0166</v>
+        <v>0.1448</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0552</v>
+        <v>0.0482</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0717</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3204</v>
+        <v>0.1237</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.3449</v>
+        <v>-0.138</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0245</v>
+        <v>0.2618</v>
       </c>
       <c r="G16" t="n">
         <v>-0.3589</v>
@@ -1702,13 +1702,13 @@
         <v>0.5792</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5407</v>
+        <v>-0.09660000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3863</v>
+        <v>-0.1794</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1544</v>
+        <v>0.0828</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.8628</v>
+        <v>-0.6215000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5521</v>
+        <v>-0.4486</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3108</v>
+        <v>-0.1729</v>
       </c>
       <c r="G17" t="n">
         <v>-0.0353</v>
@@ -1780,13 +1780,13 @@
         <v>0.5792</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4413</v>
+        <v>-0.2</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3036</v>
+        <v>-0.2001</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1378</v>
+        <v>0.0001</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1002</v>
+        <v>-0.914</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.0136</v>
+        <v>-1.1171</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.08649999999999999</v>
+        <v>0.203</v>
       </c>
       <c r="G18" t="n">
         <v>-0.1871</v>
@@ -1858,13 +1858,13 @@
         <v>1.5446</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1378</v>
+        <v>0.0483</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0279</v>
+        <v>-0.1313</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1099</v>
+        <v>0.1796</v>
       </c>
       <c r="V18" t="n">
         <v>0.5763</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.138</v>
+        <v>-1.7696</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3645</v>
+        <v>-0.256</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.5025</v>
+        <v>-1.5136</v>
       </c>
       <c r="G19" t="n">
         <v>-0.8216</v>
@@ -1936,13 +1936,13 @@
         <v>0.3862</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8108</v>
+        <v>0.1791</v>
       </c>
       <c r="T19" t="n">
-        <v>0.9099</v>
+        <v>0.2893</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.09909999999999999</v>
+        <v>-0.1102</v>
       </c>
       <c r="V19" t="n">
         <v>-1.5133</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9859</v>
+        <v>-2.2368</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5367</v>
+        <v>-0.9503</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4492</v>
+        <v>-1.2865</v>
       </c>
       <c r="G20" t="n">
         <v>-2.5441</v>
@@ -2014,13 +2014,13 @@
         <v>1.3515</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4577</v>
+        <v>0.2067</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5236</v>
+        <v>0.1099</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0659</v>
+        <v>0.0968</v>
       </c>
       <c r="V20" t="n">
         <v>-0.2856</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.4022</v>
+        <v>-2.5748</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.761</v>
+        <v>-0.3473</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.6412</v>
+        <v>-2.2275</v>
       </c>
       <c r="G21" t="n">
         <v>-1.9966</v>
@@ -2092,13 +2092,13 @@
         <v>1.7377</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8275</v>
+        <v>-0.0001</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2487</v>
+        <v>0.165</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5788</v>
+        <v>-0.1651</v>
       </c>
       <c r="V21" t="n">
         <v>-1.3505</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.0626</v>
+        <v>-5.3138</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.562</v>
+        <v>-3.2517</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.5006</v>
+        <v>-2.0621</v>
       </c>
       <c r="G22" t="n">
         <v>-4.6459</v>
@@ -2170,13 +2170,13 @@
         <v>1.9308</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0317</v>
+        <v>-0.2829</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4695</v>
+        <v>-0.1592</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5622</v>
+        <v>-0.1237</v>
       </c>
       <c r="V22" t="n">
         <v>-1.3505</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-13.4604</v>
+        <v>-10.7022</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.031</v>
+        <v>-1.0309</v>
       </c>
       <c r="F23" t="n">
-        <v>-12.4294</v>
+        <v>-9.6714</v>
       </c>
       <c r="G23" t="n">
         <v>-12.4122</v>
@@ -2248,13 +2248,13 @@
         <v>12.55</v>
       </c>
       <c r="S23" t="n">
-        <v>-3.1726</v>
+        <v>-0.4146999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5553999999999999</v>
+        <v>-0.5553</v>
       </c>
       <c r="U23" t="n">
-        <v>-2.6173</v>
+        <v>0.1405</v>
       </c>
       <c r="V23" t="n">
         <v>-0.7717000000000003</v>
